--- a/files/rules.xlsx
+++ b/files/rules.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="37">
   <si>
     <t>Rule</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>11.11.11.11</t>
-  </si>
-  <si>
-    <t>port4</t>
   </si>
   <si>
     <t>pub_host_E</t>
@@ -1754,13 +1751,13 @@
         <v>30</v>
       </c>
       <c r="E9" t="s" s="22">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s" s="22">
         <v>31</v>
       </c>
-      <c r="F9" t="s" s="22">
+      <c r="G9" t="s" s="22">
         <v>32</v>
-      </c>
-      <c r="G9" t="s" s="22">
-        <v>33</v>
       </c>
       <c r="H9" t="s" s="22">
         <v>22</v>
@@ -1786,19 +1783,19 @@
         <v>16</v>
       </c>
       <c r="C10" t="s" s="23">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s" s="23">
         <v>34</v>
       </c>
-      <c r="D10" t="s" s="23">
+      <c r="E10" t="s" s="23">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s" s="23">
         <v>35</v>
       </c>
-      <c r="E10" t="s" s="23">
-        <v>31</v>
-      </c>
-      <c r="F10" t="s" s="23">
+      <c r="G10" t="s" s="23">
         <v>36</v>
-      </c>
-      <c r="G10" t="s" s="23">
-        <v>37</v>
       </c>
       <c r="H10" t="s" s="23">
         <v>19</v>
